--- a/ics_topologies/manufacturing_plant/manufacturing_plant.xlsx
+++ b/ics_topologies/manufacturing_plant/manufacturing_plant.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,65 +445,70 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>purdue_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cvss_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>exposed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>patched</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>consequence_severity</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>awareness</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>privilege</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>p_base_override</t>
         </is>
@@ -537,49 +542,54 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Edge firewall</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Fortinet</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>FortiGate 600F</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,49 +619,54 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Core switch</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Catalyst 9300</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,49 +696,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>AD</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Windows Server 2022</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,49 +773,54 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Manufacturing Execution System</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SIMATIC IT</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -825,49 +850,54 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>ERP</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>S/4HANA</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -897,49 +927,54 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>DMZ switch</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>IE 4000</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -969,49 +1004,54 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Data historian</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>OSIsoft</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>PI Server</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1041,49 +1081,54 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>OT access</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Windows Server 2022</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1113,49 +1158,54 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Industrial Ethernet switch</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SCALANCE XM408</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1185,49 +1235,54 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Production SCADA</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>WinCC</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1257,49 +1312,54 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Operator console</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SIMATIC HMI</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1329,49 +1389,54 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Switch for welding cell</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SCALANCE XB208</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1401,49 +1466,54 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Welding cell controller</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>S7-1500</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1473,49 +1543,54 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Welding robot</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>KUKA</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>KR Cybertech</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1545,37 +1620,42 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Workpiece positioner</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>FANUC</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2-axis pos.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1609,49 +1689,54 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Switch for assembly cell</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>SCALANCE XB208</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1681,49 +1766,54 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Assembly controller</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>S7-1500</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1753,49 +1843,54 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Assembly operator panel</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>SIMATIC HMI</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1825,49 +1920,54 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Safety controller for light curtains</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>S7-1500F</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1897,37 +1997,42 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Safety light curtain</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>SICK</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>C4000</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1961,37 +2066,42 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Emergency stop</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Pilz</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>PNOZ</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2025,49 +2135,54 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>VFD for conveyor</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>ACS580</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2097,37 +2212,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Conveyor drive</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>1LA8</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2161,37 +2281,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Part presence</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Banner</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Q45</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2225,37 +2350,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Quality camera</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Cognex</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>In-Sight 7000</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2289,37 +2419,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Clamp cylinder</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>SMC</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2353,41 +2488,46 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Supervisor monitoring production lines</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2400,7 +2540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2434,6 +2574,16 @@
           <t>trust</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>firewalled</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2466,6 +2616,12 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2498,6 +2654,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2530,6 +2688,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2562,6 +2722,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2594,6 +2756,12 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2626,6 +2794,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2658,6 +2828,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2690,6 +2862,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2722,6 +2896,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2754,6 +2930,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2786,6 +2964,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2818,6 +2998,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2850,6 +3032,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2882,6 +3066,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2914,6 +3100,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2946,6 +3134,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2978,6 +3168,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3010,6 +3202,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3042,6 +3236,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3074,6 +3270,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3106,6 +3304,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3138,6 +3338,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3170,6 +3372,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3202,6 +3406,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3234,6 +3440,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3266,6 +3474,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3298,6 +3508,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
